--- a/processed_ruby_restored_xlsx/sc213_ノノ５：プール開き.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc213_ノノ５：プール開き.ss.xlsx
@@ -793,8 +793,8 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>「Yes, I've been wondering—does Youjou Academy not have
-a pool...?」</t>
+          <t>「Yes, I've been wondering—does Youjou Academy not
+have a pool...?」</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1102,8 +1102,8 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>「W-well... they do say 'seeing is believing,' so shall
-we go take a look now？」</t>
+          <t>「W-well... they do say 'seeing is believing,' so
+shall we go take a look now？」</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1364,8 +1364,8 @@
       <c r="B59" s="1" t="inlineStr">
         <is>
           <t>It's not like something that didn't exist will
-suddenly appear, but the way she still gets excited is
-cute.</t>
+suddenly appear, but the way she still gets excited
+is cute.</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -2288,8 +2288,8 @@
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>I looked at Nono-chan, who nodded cheerfully as usual,
-with a dazzled gaze.</t>
+          <t>I looked at Nono-chan, who nodded cheerfully as
+usual, with a dazzled gaze.</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2563,8 +2563,8 @@
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>As soon as I finish speaking, Nono-chan dives into the
-pool.</t>
+          <t>As soon as I finish speaking, Nono-chan dives into
+the pool.</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2624,8 +2624,8 @@
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>She sent up a big spray, then spread her arms and legs
-wide in the water to show she could float.</t>
+          <t>She sent up a big spray, then spread her arms and
+legs wide in the water to show she could float.</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2898,8 +2898,8 @@
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>「Oh wow, this is amazing... I can’t get enough—this is
-so good！」</t>
+          <t>「Oh wow, this is amazing... I can’t get enough—this
+is so good！」</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -3581,8 +3581,8 @@
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t>I couldn't hold back anymore; I tore off my clothes at
-once and bared myself completely.</t>
+          <t>I couldn't hold back anymore; I tore off my clothes
+at once and bared myself completely.</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -4055,8 +4055,8 @@
       </c>
       <c r="B235" s="1" t="inlineStr">
         <is>
-          <t>She lifts her hips and lets the penis sway gently over
-the water’s surface, and Nono-chan lets out a
+          <t>She lifts her hips and lets the penis sway gently
+over the water’s surface, and Nono-chan lets out a
 flustered, slightly panicked-sounding noise.</t>
         </is>
       </c>
@@ -4420,8 +4420,8 @@
       </c>
       <c r="B259" s="1" t="inlineStr">
         <is>
-          <t>I, having totally gotten carried away, reached my hand
-toward Nono-chan's back.</t>
+          <t>I, having totally gotten carried away, reached my
+hand toward Nono-chan's back.</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -4466,8 +4466,8 @@
       </c>
       <c r="B262" s="1" t="inlineStr">
         <is>
-          <t>When I gently set my finger there, she let out a sound
-just from that.</t>
+          <t>When I gently set my finger there, she let out a
+sound just from that.</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -4572,8 +4572,8 @@
       </c>
       <c r="B269" s="1" t="inlineStr">
         <is>
-          <t>I slowly trailed my finger from her small back down to
-her waist and then toward her butt.</t>
+          <t>I slowly trailed my finger from her small back down
+to her waist and then toward her butt.</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -4724,8 +4724,8 @@
       </c>
       <c r="B279" s="1" t="inlineStr">
         <is>
-          <t>「Yeah. I'm going to write letters on your back with my
-finger now, and you...」</t>
+          <t>「Yeah. I'm going to write letters on your back with
+my finger now, and you...」</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -4785,8 +4785,8 @@
       </c>
       <c r="B283" s="1" t="inlineStr">
         <is>
-          <t>She doesn't seem to realize this game itself is a lewd
-thing.</t>
+          <t>She doesn't seem to realize this game itself is a
+lewd thing.</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4861,8 +4861,8 @@
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
-          <t>Keeping my finger pressed to her back, I moved it from
-top to bottom, then drew a circle.</t>
+          <t>Keeping my finger pressed to her back, I moved it
+from top to bottom, then drew a circle.</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -4877,8 +4877,8 @@
       </c>
       <c r="B289" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan arched her back and moved as if to escape my
-finger.</t>
+          <t>Nono-chan arched her back and moved as if to escape
+my finger.</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -5505,8 +5505,8 @@
       <c r="B330" s="1" t="inlineStr">
         <is>
           <t>I make sure never to touch her crotch, and instead
-deliberately press only at the base of her thighs with
-my fingers.</t>
+deliberately press only at the base of her thighs
+with my fingers.</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -5842,8 +5842,8 @@
       </c>
       <c r="B352" s="1" t="inlineStr">
         <is>
-          <t>「Ja- Janitor-sensei！ P-please stop... someone will see
-us...」</t>
+          <t>「Ja- Janitor-sensei！ P-please stop... someone will
+see us...」</t>
         </is>
       </c>
       <c r="C352" t="n">
@@ -6122,8 +6122,8 @@
       </c>
       <c r="B370" s="1" t="inlineStr">
         <is>
-          <t>She has to hold back her voice, and Nono-chan lets out
-muffled breaths.</t>
+          <t>She has to hold back her voice, and Nono-chan lets
+out muffled breaths.</t>
         </is>
       </c>
       <c r="C370" t="n">
@@ -6154,8 +6154,8 @@
       </c>
       <c r="B372" s="1" t="inlineStr">
         <is>
-          <t>Or maybe she just happens to be feeling exactly what I
-wrote on her back.</t>
+          <t>Or maybe she just happens to be feeling exactly what
+I wrote on her back.</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -6486,8 +6486,8 @@
       </c>
       <c r="B394" s="1" t="inlineStr">
         <is>
-          <t>「W-why does it come to that...? Yo-Muin-sensei made me
-say that...!」</t>
+          <t>「W-why does it come to that...? Yo-Muin-sensei made
+me say that...!」</t>
         </is>
       </c>
       <c r="C394" t="n">
@@ -7273,7 +7273,8 @@
       </c>
       <c r="B445" s="1" t="inlineStr">
         <is>
-          <t>I keep pinching her nipple and roll it as I stroke it.</t>
+          <t>I keep pinching her nipple and roll it as I stroke
+it.</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -7288,8 +7289,8 @@
       </c>
       <c r="B446" s="1" t="inlineStr">
         <is>
-          <t>Even in the pool's cool water, Nono-chan's body warmth
-comes through clearly.</t>
+          <t>Even in the pool's cool water, Nono-chan's body
+warmth comes through clearly.</t>
         </is>
       </c>
       <c r="C446" t="n">
@@ -7335,8 +7336,8 @@
       </c>
       <c r="B449" s="1" t="inlineStr">
         <is>
-          <t>「Mmm-mmm... I hear Rurichiyo would be in a fix without
-that... I want to get it to her right away！」</t>
+          <t>「Mmm-mmm... I hear Rurichiyo would be in a fix
+without that... I want to get it to her right away！」</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -7457,8 +7458,8 @@
       </c>
       <c r="B457" s="1" t="inlineStr">
         <is>
-          <t>But their voices and presence immediately drifted away
-again.</t>
+          <t>But their voices and presence immediately drifted
+away again.</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -7641,8 +7642,8 @@
       <c r="B469" s="1" t="inlineStr">
         <is>
           <t>We'd been doing dirty things up until now, then
-suddenly went back to the game, so she probably didn't
-know what was going on.</t>
+suddenly went back to the game, so she probably
+didn't know what was going on.</t>
         </is>
       </c>
       <c r="C469" t="n">
@@ -7657,7 +7658,8 @@
       </c>
       <c r="B470" s="1" t="inlineStr">
         <is>
-          <t>...But right now I didn't want her to make any sounds.</t>
+          <t>...But right now I didn't want her to make any
+sounds.</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -7962,8 +7964,8 @@
       </c>
       <c r="B490" s="1" t="inlineStr">
         <is>
-          <t>Then I stroke the slit over the swimsuit, and it feels
-damp and hot.</t>
+          <t>Then I stroke the slit over the swimsuit, and it
+feels damp and hot.</t>
         </is>
       </c>
       <c r="C490" t="n">
@@ -7978,7 +7980,8 @@
       </c>
       <c r="B491" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan's pussy already seems to be perfectly ready.</t>
+          <t>Nono-chan's pussy already seems to be perfectly
+ready.</t>
         </is>
       </c>
       <c r="C491" t="n">
@@ -8312,8 +8315,8 @@
       </c>
       <c r="B513" s="1" t="inlineStr">
         <is>
-          <t>It squeezes me tightly, as if trying to expel my penis
-as a foreign object.</t>
+          <t>It squeezes me tightly, as if trying to expel my
+penis as a foreign object.</t>
         </is>
       </c>
       <c r="C513" t="n">
@@ -8420,8 +8423,8 @@
       </c>
       <c r="B520" s="1" t="inlineStr">
         <is>
-          <t>「Faaaah… nn！ M-my voice, no… no no… it’s going to come
-out…！」</t>
+          <t>「Faaaah… nn！ M-my voice, no… no no… it’s going to
+come out…！」</t>
         </is>
       </c>
       <c r="C520" t="n">
@@ -8608,8 +8611,8 @@
       </c>
       <c r="B532" s="1" t="inlineStr">
         <is>
-          <t>Maybe because her body is so well-developed, her other
-senses are sharpened too.</t>
+          <t>Maybe because her body is so well-developed, her
+other senses are sharpened too.</t>
         </is>
       </c>
       <c r="C532" t="n">
@@ -9026,8 +9029,8 @@
       </c>
       <c r="B559" s="1" t="inlineStr">
         <is>
-          <t>I wanted Nono-chan to feel plenty good, so it was time
-to make her give in.</t>
+          <t>I wanted Nono-chan to feel plenty good, so it was
+time to make her give in.</t>
         </is>
       </c>
       <c r="C559" t="n">
@@ -9303,8 +9306,8 @@
       <c r="B577" s="1" t="inlineStr">
         <is>
           <t>If she tries to steady her breathing a sound slips
-out, and if she keeps her mouth closed her breath gets
-choked off.</t>
+out, and if she keeps her mouth closed her breath
+gets choked off.</t>
         </is>
       </c>
       <c r="C577" t="n">
@@ -9792,7 +9795,8 @@
       </c>
       <c r="B609" s="1" t="inlineStr">
         <is>
-          <t>「But I rather like it as it is; I'm attached to it...」</t>
+          <t>「But I rather like it as it is; I'm attached to
+it...」</t>
         </is>
       </c>
       <c r="C609" t="n">
@@ -9822,9 +9826,9 @@
       </c>
       <c r="B611" s="1" t="inlineStr">
         <is>
-          <t>「Yeah... well, a building only really counts when it's
-being used... even if it's old, it seems well taken
-care of.」</t>
+          <t>「Yeah... well, a building only really counts when
+it's being used... even if it's old, it seems well
+taken care of.」</t>
         </is>
       </c>
       <c r="C611" t="n">
@@ -10450,7 +10454,8 @@
       </c>
       <c r="B652" s="1" t="inlineStr">
         <is>
-          <t>「Ah！ Aah！ Y-you…Muiin, sensei...！ Nfuu！ Soft... hey！？」</t>
+          <t>「Ah！ Aah！ Y-you…Muiin, sensei...！ Nfuu！ Soft...
+hey！？」</t>
         </is>
       </c>
       <c r="C652" t="n">
@@ -10716,7 +10721,8 @@
       <c r="B669" s="1" t="inlineStr">
         <is>
           <t>Even though I'm the one touching, I even get the
-illusion that her breasts are suctioning onto my palm.</t>
+illusion that her breasts are suctioning onto my
+palm.</t>
         </is>
       </c>
       <c r="C669" t="n">
@@ -10931,7 +10937,8 @@
       </c>
       <c r="B683" s="1" t="inlineStr">
         <is>
-          <t>「Hah, hah...! Nnhh! Ah, ah...! W-wait... p-please...!」</t>
+          <t>「Hah, hah...! Nnhh! Ah, ah...! W-wait...
+p-please...!」</t>
         </is>
       </c>
       <c r="C683" t="n">
@@ -11070,9 +11077,9 @@
       </c>
       <c r="B692" s="1" t="inlineStr">
         <is>
-          <t>Pleasure spiked all at once, and I just thrust my hips
-back and forth… no—there wasn’t even room to think
-about doing that, I just kept thrusting！</t>
+          <t>Pleasure spiked all at once, and I just thrust my
+hips back and forth… no—there wasn’t even room to
+think about doing that, I just kept thrusting！</t>
         </is>
       </c>
       <c r="C692" t="n">
@@ -11274,8 +11281,8 @@
       </c>
       <c r="B705" s="1" t="inlineStr">
         <is>
-          <t>「Wah！ U-uh！ Nn-ahh, ha！ No—！ I'm gonna... come...！ Nn！
-Nn—！！」</t>
+          <t>「Wah！ U-uh！ Nn-ahh, ha！ No—！ I'm gonna... come...！
+Nn！ Nn—！！」</t>
         </is>
       </c>
       <c r="C705" t="n">
@@ -11670,8 +11677,8 @@
       </c>
       <c r="B731" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan’s hips sink and she ends up falling into the
-pool.</t>
+          <t>Nono-chan’s hips sink and she ends up falling into
+the pool.</t>
         </is>
       </c>
       <c r="C731" t="n">
@@ -11795,8 +11802,8 @@
       </c>
       <c r="B739" s="1" t="inlineStr">
         <is>
-          <t>At this point, I have no idea what else could be mixed
-into the water in this pool.</t>
+          <t>At this point, I have no idea what else could be
+mixed into the water in this pool.</t>
         </is>
       </c>
       <c r="C739" t="n">
@@ -12010,8 +12017,8 @@
       </c>
       <c r="B753" s="1" t="inlineStr">
         <is>
-          <t>「My heart was racing partway through, but actually, it
-might've felt even better because of that...？」</t>
+          <t>「My heart was racing partway through, but actually,
+it might've felt even better because of that...？」</t>
         </is>
       </c>
       <c r="C753" t="n">
@@ -12041,8 +12048,8 @@
       </c>
       <c r="B755" s="1" t="inlineStr">
         <is>
-          <t>「Y-yes... nn, fuuu...！ Haa, ahhaa... I got all excited
-too...」</t>
+          <t>「Y-yes... nn, fuuu...！ Haa, ahhaa... I got all
+excited too...」</t>
         </is>
       </c>
       <c r="C755" t="n">
@@ -12624,8 +12631,8 @@
       </c>
       <c r="B793" s="1" t="inlineStr">
         <is>
-          <t>There stood Kikuchiyo-baa-chan, who should have left a
-little while ago.</t>
+          <t>There stood Kikuchiyo-baa-chan, who should have left
+a little while ago.</t>
         </is>
       </c>
       <c r="C793" t="n">
@@ -12779,8 +12786,8 @@
       </c>
       <c r="B803" s="1" t="inlineStr">
         <is>
-          <t>...A danger signal was blaring in my head, and I could
-only give a half-hearted reply.</t>
+          <t>...A danger signal was blaring in my head, and I
+could only give a half-hearted reply.</t>
         </is>
       </c>
       <c r="C803" t="n">
@@ -12810,8 +12817,8 @@
       </c>
       <c r="B805" s="1" t="inlineStr">
         <is>
-          <t>「Ah, um… nnh, nnhh！ Director Kikuchiyo？ Today… why are
-you here…？」</t>
+          <t>「Ah, um… nnh, nnhh！ Director Kikuchiyo？ Today… why
+are you here…？」</t>
         </is>
       </c>
       <c r="C805" t="n">
@@ -12842,8 +12849,8 @@
       </c>
       <c r="B807" s="1" t="inlineStr">
         <is>
-          <t>She probably won't listen to my explanation, but maybe
-Nono-chan can somehow fix this.</t>
+          <t>She probably won't listen to my explanation, but
+maybe Nono-chan can somehow fix this.</t>
         </is>
       </c>
       <c r="C807" t="n">
@@ -13012,8 +13019,8 @@
       </c>
       <c r="B818" s="1" t="inlineStr">
         <is>
-          <t>「What are you saying？ If you’re all kyakya—wanwan like
-that, even if I don’t want to I’ll hear it…！」</t>
+          <t>「What are you saying？ If you’re all kyakya—wanwan
+like that, even if I don’t want to I’ll hear it…！」</t>
         </is>
       </c>
       <c r="C818" t="n">
@@ -13058,8 +13065,8 @@
       </c>
       <c r="B821" s="1" t="inlineStr">
         <is>
-          <t>Hearing Kikuchiyo-baa-chan’s words, my head goes white
-again.</t>
+          <t>Hearing Kikuchiyo-baa-chan’s words, my head goes
+white again.</t>
         </is>
       </c>
       <c r="C821" t="n">
@@ -13180,9 +13187,9 @@
       </c>
       <c r="B829" s="1" t="inlineStr">
         <is>
-          <t>Her tone acts like she hasn’t noticed we were enjoying
-ourselves in a different way, but did she just say
-something outrageous again！？</t>
+          <t>Her tone acts like she hasn’t noticed we were
+enjoying ourselves in a different way, but did she
+just say something outrageous again！？</t>
         </is>
       </c>
       <c r="C829" t="n">
@@ -13259,8 +13266,8 @@
       </c>
       <c r="B834" s="1" t="inlineStr">
         <is>
-          <t>When I suddenly blurted that out, Nono-chan went along
-with it.</t>
+          <t>When I suddenly blurted that out, Nono-chan went
+along with it.</t>
         </is>
       </c>
       <c r="C834" t="n">
@@ -13335,8 +13342,8 @@
       </c>
       <c r="B839" s="1" t="inlineStr">
         <is>
-          <t>Kikuchiyo-baa-chan, who has far too much confidence in
-how young she looks, wouldn't listen even to
+          <t>Kikuchiyo-baa-chan, who has far too much confidence
+in how young she looks, wouldn't listen even to
 Nono-chan's persuasion.</t>
         </is>
       </c>
@@ -13352,7 +13359,8 @@
       </c>
       <c r="B840" s="1" t="inlineStr">
         <is>
-          <t>I, belatedly, thought back over the current situation.</t>
+          <t>I, belatedly, thought back over the current
+situation.</t>
         </is>
       </c>
       <c r="C840" t="n">
@@ -13584,7 +13592,8 @@
       </c>
       <c r="B855" s="1" t="inlineStr">
         <is>
-          <t>The principal's perfectly timed announcement saved us.</t>
+          <t>The principal's perfectly timed announcement saved
+us.</t>
         </is>
       </c>
       <c r="C855" t="n">
@@ -13614,7 +13623,8 @@
       </c>
       <c r="B857" s="1" t="inlineStr">
         <is>
-          <t>「Hmm... it can't be helped！ We'll do it another time.」</t>
+          <t>「Hmm... it can't be helped！ We'll do it another
+time.」</t>
         </is>
       </c>
       <c r="C857" t="n">
@@ -13872,9 +13882,9 @@
       </c>
       <c r="B874" s="1" t="inlineStr">
         <is>
-          <t>But we stayed connected and I felt this weird tension,
-and to be honest I suddenly got hit with a rush of
-exhaustion...</t>
+          <t>But we stayed connected and I felt this weird
+tension, and to be honest I suddenly got hit with a
+rush of exhaustion...</t>
         </is>
       </c>
       <c r="C874" t="n">
@@ -13996,8 +14006,8 @@
       </c>
       <c r="B882" s="1" t="inlineStr">
         <is>
-          <t>When Nono-chan smiled like she always does, I felt all
-warm and fuzzy.</t>
+          <t>When Nono-chan smiled like she always does, I felt
+all warm and fuzzy.</t>
         </is>
       </c>
       <c r="C882" t="n">

--- a/processed_ruby_restored_xlsx/sc213_ノノ５：プール開き.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc213_ノノ５：プール開き.ss.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>「Janitor-sensei, can I have a moment？」</t>
+          <t>Janitor-sensei, can I have a moment？</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1102,8 +1102,8 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>「W-well... they do say 'seeing is believing,' so
-shall we go take a look now？」</t>
+          <t>W-well... they do say 'seeing is believing,' so shall
+we go take a look now？</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>「Ah...！ Is that really okay！？」</t>
+          <t>Ah...！ Is that really okay！？</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1425,8 +1425,8 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>「Ooh... this is Janitor-sensei's secret room, isn't
-it？」</t>
+          <t>Ooh... this is Janitor-sensei's secret room, isn't
+it？</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1488,8 +1488,8 @@
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>「A Janitor-sensei room was a blind spot... Is there a
-hidden door？ Or stairs leading down to a basement...」</t>
+          <t>A Janitor-sensei room was a blind spot... Is there a
+hidden door？ Or stairs leading down to a basement...</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>「O-oh... as expected of Janitor-sensei！」</t>
+          <t>O-oh... as expected of Janitor-sensei！</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>When I added that, thinking she'd be pleased, I got
+          <t>When I added that, thinking they'd be pleased, I got
 the expected—or rather, even bigger—reaction.</t>
         </is>
       </c>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>「Fwaaah~！ This feels so good…！」</t>
+          <t>Fwaaah~！ This feels so good…！</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2624,8 +2624,8 @@
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>She sent up a big spray, then spread her arms and
-legs wide in the water to show she could float.</t>
+          <t>They sent up a big spray, then spread their arms and
+legs wide in the water to show they could float.</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>「Mmm~ fuu~！ Fufuu~♪」</t>
+          <t>Mmm~ fuu~！ Fufuu~♪</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="B216" s="1" t="inlineStr">
         <is>
-          <t>Even so, the heat of arousal didn’t die down, and my
+          <t>Even so, the heat of arousal didn’t die down, and his
 penis arched up and pulsed.</t>
         </is>
       </c>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="B229" s="1" t="inlineStr">
         <is>
-          <t>「Aah...uuh...！ I-I can't... deny it...」</t>
+          <t>Aah...uuh...！ I-I can't... deny it...</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="B232" s="1" t="inlineStr">
         <is>
-          <t>「I was looking at Nono… see, I just couldn’t hold
+          <t>「I was looking at Monono… see, I just couldn’t hold
 myself back.」</t>
         </is>
       </c>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="B234" s="1" t="inlineStr">
         <is>
-          <t>「Nnngh!？　Nnhh？!!　Foaah!？」</t>
+          <t>Nnngh!？　Nnhh？!!　Foaah!？</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B317" s="1" t="inlineStr">
         <is>
-          <t>「Aah... Janitor-sensei...」</t>
+          <t>Aah... Janitor-sensei...</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -5842,8 +5842,8 @@
       </c>
       <c r="B352" s="1" t="inlineStr">
         <is>
-          <t>「Ja- Janitor-sensei！ P-please stop... someone will
-see us...」</t>
+          <t>Ja- Janitor-sensei！ P-please stop... someone will see
+us...</t>
         </is>
       </c>
       <c r="C352" t="n">
@@ -5952,8 +5952,8 @@
       </c>
       <c r="B359" s="1" t="inlineStr">
         <is>
-          <t>「It's fine... We're just simulating the pool opening,
-so there's no problem, right？」</t>
+          <t>It's fine... We're just simulating the pool opening,
+so there's no problem, right？</t>
         </is>
       </c>
       <c r="C359" t="n">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="B361" s="1" t="inlineStr">
         <is>
-          <t>「Nnngh~ but... bu-but...！」</t>
+          <t>Nnngh~ but... bu-but...！</t>
         </is>
       </c>
       <c r="C361" t="n">
@@ -6029,8 +6029,8 @@
       </c>
       <c r="B364" s="1" t="inlineStr">
         <is>
-          <t>「Okay, then continuing with question two... here we
-go...！」</t>
+          <t>Okay, then continuing with question two... here we
+go...！</t>
         </is>
       </c>
       <c r="C364" t="n">
@@ -6060,7 +6060,7 @@
       </c>
       <c r="B366" s="1" t="inlineStr">
         <is>
-          <t>「Hah, ha...！ Fai！」</t>
+          <t>Hah, ha...！ Fai！</t>
         </is>
       </c>
       <c r="C366" t="n">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="B369" s="1" t="inlineStr">
         <is>
-          <t>「Nn... nngh！ nn...！ nngh...！ fuuuu... uuuh... nn...！」</t>
+          <t>Nn... nngh！ nn...！ nngh...！ fuuuu... uuuh... nn...！</t>
         </is>
       </c>
       <c r="C369" t="n">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="B374" s="1" t="inlineStr">
         <is>
-          <t>「Okay！ Answer, please.」</t>
+          <t>Okay！ Answer, please.</t>
         </is>
       </c>
       <c r="C374" t="n">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="B376" s="1" t="inlineStr">
         <is>
-          <t>「...E-ecchi... is it...？」</t>
+          <t>...E-ecchi... is it...？</t>
         </is>
       </c>
       <c r="C376" t="n">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="B378" s="1" t="inlineStr">
         <is>
-          <t>「Heh heh, woohoo... correct！ Alright, one more！」</t>
+          <t>Heh heh, woohoo... correct！ Alright, one more！</t>
         </is>
       </c>
       <c r="C378" t="n">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="B380" s="1" t="inlineStr">
         <is>
-          <t>「Nn...！ Nnfu...！ nn... nngh！ u... ufuu... fuuu...！」</t>
+          <t>Nn...！ Nnfu...！ nn... nngh！ u... ufuu... fuuu...！</t>
         </is>
       </c>
       <c r="C380" t="n">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="B382" s="1" t="inlineStr">
         <is>
-          <t>「Okay, this time...？」</t>
+          <t>Okay, this time...？</t>
         </is>
       </c>
       <c r="C382" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="B384" s="1" t="inlineStr">
         <is>
-          <t>「I... I want to...」</t>
+          <t>I... I want to...</t>
         </is>
       </c>
       <c r="C384" t="n">
@@ -6532,8 +6532,8 @@
       </c>
       <c r="B397" s="1" t="inlineStr">
         <is>
-          <t>Forcing it into that story, I place both hands on her
-chest and start feeling through the swimsuit.</t>
+          <t>Forcing it into that story, he places both hands on
+her chest and starts feeling through the swimsuit.</t>
         </is>
       </c>
       <c r="C397" t="n">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="B404" s="1" t="inlineStr">
         <is>
-          <t>Thinking that's a relief, I begin to stimulate
+          <t>Thinking that's a relief, he begins to stimulate
 Nono-chan's tiny chest as if massaging it.</t>
         </is>
       </c>
@@ -6687,7 +6687,8 @@
       </c>
       <c r="B407" s="1" t="inlineStr">
         <is>
-          <t>With the palms of my hands, I knead slowly, slowly.</t>
+          <t>With the palms of his hands, he kneads slowly,
+slowly.</t>
         </is>
       </c>
       <c r="C407" t="n">
@@ -6702,8 +6703,8 @@
       </c>
       <c r="B408" s="1" t="inlineStr">
         <is>
-          <t>Then I firmly confirm the irresistibly smooth feel of
-the swimsuit against her soft chest.</t>
+          <t>Then he firmly confirms the irresistibly smooth feel
+of the swimsuit against her soft chest.</t>
         </is>
       </c>
       <c r="C408" t="n">
@@ -6872,8 +6873,8 @@
       </c>
       <c r="B419" s="1" t="inlineStr">
         <is>
-          <t>She probably thinks she's holding back, but her voice
-is gradually getting louder.</t>
+          <t>They probably think they're holding back, but their
+voice is gradually getting louder.</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -6964,7 +6965,7 @@
       </c>
       <c r="B425" s="1" t="inlineStr">
         <is>
-          <t>「Gah, I have to... I have to hold it in...！」</t>
+          <t>Gah, I have to... I have to hold it in...！</t>
         </is>
       </c>
       <c r="C425" t="n">
@@ -7026,7 +7027,7 @@
       </c>
       <c r="B429" s="1" t="inlineStr">
         <is>
-          <t>「Nn, nfu... nnn aaahhhhh...！」</t>
+          <t>Nn, nfu... nnn aaahhhhh...！</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -7443,7 +7444,7 @@
       </c>
       <c r="B456" s="1" t="inlineStr">
         <is>
-          <t>It came back...！？</t>
+          <t>It came back...！？"</t>
         </is>
       </c>
       <c r="C456" t="n">
@@ -7459,7 +7460,7 @@
       <c r="B457" s="1" t="inlineStr">
         <is>
           <t>But their voices and presence immediately drifted
-away again.</t>
+away again."</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -7504,7 +7505,7 @@
       </c>
       <c r="B460" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan called out with a puzzled look.</t>
+          <t>Nono-chan called out with a puzzled look."</t>
         </is>
       </c>
       <c r="C460" t="n">
@@ -7520,7 +7521,7 @@
       <c r="B461" s="1" t="inlineStr">
         <is>
           <t>...I wonder if Nono-chan heard Kikuchiyo-baa-chan and
-the others' voices.</t>
+the others' voices."</t>
         </is>
       </c>
       <c r="C461" t="n">
@@ -7536,7 +7537,7 @@
       <c r="B462" s="1" t="inlineStr">
         <is>
           <t>Or did she find it suspicious that I suddenly stopped
-moving...</t>
+moving..."</t>
         </is>
       </c>
       <c r="C462" t="n">
@@ -7551,7 +7552,7 @@
       </c>
       <c r="B463" s="1" t="inlineStr">
         <is>
-          <t>In any case, I didn't want to break the momentum.</t>
+          <t>In any case, I didn't want to break the momentum."</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -7626,7 +7627,7 @@
       </c>
       <c r="B468" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan looked bewildered.</t>
+          <t>Nono-chan looked bewildered."</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -7643,7 +7644,7 @@
         <is>
           <t>We'd been doing dirty things up until now, then
 suddenly went back to the game, so she probably
-didn't know what was going on.</t>
+didn't know what was going on."</t>
         </is>
       </c>
       <c r="C469" t="n">
@@ -7659,7 +7660,7 @@
       <c r="B470" s="1" t="inlineStr">
         <is>
           <t>...But right now I didn't want her to make any
-sounds.</t>
+sounds."</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -7676,7 +7677,7 @@
         <is>
           <t>I said I'd give a question, but instead I just
 pretended to write on her back, tracing it with my
-finger to make it look convincing.</t>
+finger to make it look convincing."</t>
         </is>
       </c>
       <c r="C471" t="n">
@@ -7782,7 +7783,7 @@
       </c>
       <c r="B478" s="1" t="inlineStr">
         <is>
-          <t>Nono-chan squeezed her eyes shut.</t>
+          <t>Nono-chan squeezed her eyes shut."</t>
         </is>
       </c>
       <c r="C478" t="n">
@@ -7797,7 +7798,8 @@
       </c>
       <c r="B479" s="1" t="inlineStr">
         <is>
-          <t>She seemed to be imagining the thing she wanted most.</t>
+          <t>She seemed to be imagining the thing she wanted
+most."</t>
         </is>
       </c>
       <c r="C479" t="n">
@@ -7812,7 +7814,7 @@
       </c>
       <c r="B480" s="1" t="inlineStr">
         <is>
-          <t>...And after hesitating, she opened her mouth.</t>
+          <t>...And after hesitating, she opened her mouth."</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -7949,7 +7951,8 @@
       </c>
       <c r="B489" s="1" t="inlineStr">
         <is>
-          <t>I lower my finger down and gently touches her pussy.</t>
+          <t>He lowers his finger down and gently touches her
+pussy.</t>
         </is>
       </c>
       <c r="C489" t="n">
@@ -7964,7 +7967,7 @@
       </c>
       <c r="B490" s="1" t="inlineStr">
         <is>
-          <t>Then I stroke the slit over the swimsuit, and it
+          <t>Then he strokes the slit over the swimsuit, and it
 feels damp and hot.</t>
         </is>
       </c>
@@ -8102,8 +8105,8 @@
       </c>
       <c r="B499" s="1" t="inlineStr">
         <is>
-          <t>Riding the rush of excitement, I thrust my penis all
-the way in at once.</t>
+          <t>Riding the rush of excitement, he thrusts his penis
+all the way in at once.</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -8315,7 +8318,7 @@
       </c>
       <c r="B513" s="1" t="inlineStr">
         <is>
-          <t>It squeezes me tightly, as if trying to expel my
+          <t>It squeezes him tightly, as if trying to expel his
 penis as a foreign object.</t>
         </is>
       </c>
@@ -8533,8 +8536,8 @@
       </c>
       <c r="B527" s="1" t="inlineStr">
         <is>
-          <t>「Nnh！ Ja- Janitor-sensei...！ A loud noise is
-escaping... nnngh」</t>
+          <t>Nnh！ Ja- Janitor-sensei...！ A loud noise is
+escaping... nnngh</t>
         </is>
       </c>
       <c r="C527" t="n">
@@ -8735,8 +8738,8 @@
       </c>
       <c r="B540" s="1" t="inlineStr">
         <is>
-          <t>To make my penis glide better, copious wetness leaked
-out from deep inside.</t>
+          <t>To make her penis glide better, copious wetness
+leaked out from deep inside.</t>
         </is>
       </c>
       <c r="C540" t="n">
@@ -8782,7 +8785,7 @@
       </c>
       <c r="B543" s="1" t="inlineStr">
         <is>
-          <t>「Ah！ Uuh... mgh！」</t>
+          <t>Ah！ Uuh... mgh！</t>
         </is>
       </c>
       <c r="C543" t="n">
@@ -8843,8 +8846,8 @@
       </c>
       <c r="B547" s="1" t="inlineStr">
         <is>
-          <t>「…If you do that, I think it'll just make it harder
-for you to hold back...」</t>
+          <t>…If you do that, I think it'll just make it harder
+for you to hold back...</t>
         </is>
       </c>
       <c r="C547" t="n">
@@ -8874,7 +8877,7 @@
       </c>
       <c r="B549" s="1" t="inlineStr">
         <is>
-          <t>「Nn！ Nn~！ Nng, fguu！」</t>
+          <t>Nn！ Nn~！ Nng, fguu！</t>
         </is>
       </c>
       <c r="C549" t="n">
@@ -8936,7 +8939,7 @@
       </c>
       <c r="B553" s="1" t="inlineStr">
         <is>
-          <t>「Nbu！ Buf！ Bugu... bukubuku！」</t>
+          <t>Nbu！ Buf！ Bugu... bukubuku！</t>
         </is>
       </c>
       <c r="C553" t="n">
@@ -8998,7 +9001,7 @@
       </c>
       <c r="B557" s="1" t="inlineStr">
         <is>
-          <t>「Bububu！ Bukkubuku！ Ugugu funn！」</t>
+          <t>Bububu！ Bukkubuku！ Ugugu funn！</t>
         </is>
       </c>
       <c r="C557" t="n">
@@ -9076,7 +9079,7 @@
       </c>
       <c r="B562" s="1" t="inlineStr">
         <is>
-          <t>「Puhahh！」</t>
+          <t>Puhahh！</t>
         </is>
       </c>
       <c r="C562" t="n">
@@ -9122,7 +9125,7 @@
       </c>
       <c r="B565" s="1" t="inlineStr">
         <is>
-          <t>「Haaah！　Fuu！　Fuu！　Faaah...！」</t>
+          <t>Haaah！　Fuu！　Fuu！　Faaah...！</t>
         </is>
       </c>
       <c r="C565" t="n">
@@ -9274,7 +9277,7 @@
       </c>
       <c r="B575" s="1" t="inlineStr">
         <is>
-          <t>「Hah！ Haa... fuu... nngh！ Nfuh！ Haa, hafaa...」</t>
+          <t>Hah！ Haa... fuu... nngh！ Nfuh！ Haa, hafaa...</t>
         </is>
       </c>
       <c r="C575" t="n">
@@ -9289,7 +9292,7 @@
       </c>
       <c r="B576" s="1" t="inlineStr">
         <is>
-          <t>But by now it's probably too hard to keep her mouth
+          <t>But by now it's probably too hard to keep their mouth
 shut.</t>
         </is>
       </c>
@@ -9305,8 +9308,8 @@
       </c>
       <c r="B577" s="1" t="inlineStr">
         <is>
-          <t>If she tries to steady her breathing a sound slips
-out, and if she keeps her mouth closed her breath
+          <t>If they try to steady their breathing a sound slips
+out, and if they keep their mouth closed their breath
 gets choked off.</t>
         </is>
       </c>
@@ -9858,8 +9861,8 @@
       </c>
       <c r="B613" s="1" t="inlineStr">
         <is>
-          <t>「That's thanks to the excellent Janitor-san, after
-all.」</t>
+          <t>That's thanks to the excellent Janitor-san, after
+all.</t>
         </is>
       </c>
       <c r="C613" t="n">
@@ -9889,8 +9892,8 @@
       </c>
       <c r="B615" s="1" t="inlineStr">
         <is>
-          <t>「Ja- Janitor-sensei！ You're being praised！ You're
-being praised...！」</t>
+          <t>Ja- Janitor-sensei！ You're being praised！ You're
+being praised...！</t>
         </is>
       </c>
       <c r="C615" t="n">
@@ -10059,7 +10062,7 @@
       </c>
       <c r="B626" s="1" t="inlineStr">
         <is>
-          <t>「Ja- Janitor-senseeeeee...！」</t>
+          <t>Ja- Janitor-senseeeeee...！</t>
         </is>
       </c>
       <c r="C626" t="n">
@@ -10470,7 +10473,7 @@
       </c>
       <c r="B653" s="1" t="inlineStr">
         <is>
-          <t>I slip my hand in from her shoulder and slide it
+          <t>He slips his hand in from her shoulder and slides it
 inside her swimsuit.</t>
         </is>
       </c>
@@ -10486,7 +10489,7 @@
       </c>
       <c r="B654" s="1" t="inlineStr">
         <is>
-          <t>Then I go on to touch her breasts directly.</t>
+          <t>Then he goes on to touch her breasts directly.</t>
         </is>
       </c>
       <c r="C654" t="n">
@@ -10547,7 +10550,7 @@
       </c>
       <c r="B658" s="1" t="inlineStr">
         <is>
-          <t>Also, her body — especially her pussy — has gotten
+          <t>Also, my body — especially my pussy — has gotten
 pretty loose.</t>
         </is>
       </c>
@@ -10608,8 +10611,8 @@
       </c>
       <c r="B662" s="1" t="inlineStr">
         <is>
-          <t>「Uuu... Aaah, a-guu！ It feels so good... I'm...
-getting too much... Nn！ Kuu...」</t>
+          <t>Uuu... Aaah, a-guu！ It feels so good... I」m...
+getting too much... Nn！ Kuu...</t>
         </is>
       </c>
       <c r="C662" t="n">
@@ -10937,8 +10940,7 @@
       </c>
       <c r="B683" s="1" t="inlineStr">
         <is>
-          <t>「Hah, hah...! Nnhh! Ah, ah...! W-wait...
-p-please...!」</t>
+          <t>Hah, hah...! Nnhh! Ah, ah...! W-wait... p-please...!</t>
         </is>
       </c>
       <c r="C683" t="n">
@@ -10968,8 +10970,8 @@
       </c>
       <c r="B685" s="1" t="inlineStr">
         <is>
-          <t>And yet, her pussy was squeezing my penis so tight it
-might've been the tightest all day.</t>
+          <t>And yet, her pussy was squeezing his penis so tight
+it might've been the tightest all day.</t>
         </is>
       </c>
       <c r="C685" t="n">
@@ -11109,8 +11111,8 @@
       </c>
       <c r="B694" s="1" t="inlineStr">
         <is>
-          <t>「Ugh！ Ah！ Janitor-sensei！ Nn！ N-no！ If you keep doing
-that to me now...」</t>
+          <t>Ugh！ Ah！ Janitor-sensei！ Nn！ N-no！ If you keep doing
+that to me now...</t>
         </is>
       </c>
       <c r="C694" t="n">
@@ -11188,8 +11190,8 @@
       </c>
       <c r="B699" s="1" t="inlineStr">
         <is>
-          <t>Spraying up huge splashes, I drive my penis into the
-depths of her pussy.</t>
+          <t>Spraying up huge splashes, he drives his penis into
+the depths of her pussy.</t>
         </is>
       </c>
       <c r="C699" t="n">
@@ -11281,8 +11283,8 @@
       </c>
       <c r="B705" s="1" t="inlineStr">
         <is>
-          <t>「Wah！ U-uh！ Nn-ahh, ha！ No—！ I'm gonna... come...！
-Nn！ Nn—！！」</t>
+          <t>Wah！ U-uh！ Nn-ahh, ha！ No—！ I'm gonna... come...！ Nn！
+Nn—！！</t>
         </is>
       </c>
       <c r="C705" t="n">
@@ -11600,7 +11602,7 @@
       </c>
       <c r="B726" s="1" t="inlineStr">
         <is>
-          <t>「Waaaaahhh... aaahhh...！」</t>
+          <t>Waaaaahhh... aaahhh...！</t>
         </is>
       </c>
       <c r="C726" t="n">
@@ -12048,8 +12050,8 @@
       </c>
       <c r="B755" s="1" t="inlineStr">
         <is>
-          <t>「Y-yes... nn, fuuu...！ Haa, ahhaa... I got all
-excited too...」</t>
+          <t>Y-yes... nn, fuuu...！ Haa, ahhaa... I got all excited
+too...</t>
         </is>
       </c>
       <c r="C755" t="n">
@@ -12111,8 +12113,8 @@
       </c>
       <c r="B759" s="1" t="inlineStr">
         <is>
-          <t>「Heh... maybe the ones being watched are the ones who
-end up feeling it, you know？」</t>
+          <t>Heh... maybe the ones being watched are the ones who
+end up feeling it, you know？</t>
         </is>
       </c>
       <c r="C759" t="n">
@@ -12142,7 +12144,7 @@
       </c>
       <c r="B761" s="1" t="inlineStr">
         <is>
-          <t>「Uuu... nmm！ Th-that's absolutely not true...！」</t>
+          <t>Uuu... nmm！ Th-that's absolutely not true...！</t>
         </is>
       </c>
       <c r="C761" t="n">
@@ -12218,7 +12220,7 @@
       </c>
       <c r="B766" s="1" t="inlineStr">
         <is>
-          <t>「M-muu... Janitor-sensei is being mean...」</t>
+          <t>M-muu... Janitor-sensei is being mean...</t>
         </is>
       </c>
       <c r="C766" t="n">
@@ -12369,7 +12371,7 @@
       </c>
       <c r="B776" s="1" t="inlineStr">
         <is>
-          <t>It felt like it was over like that, but my penis was
+          <t>It felt like it was over like that, but his penis was
 still inside.</t>
         </is>
       </c>
@@ -12446,7 +12448,7 @@
       </c>
       <c r="B781" s="1" t="inlineStr">
         <is>
-          <t>After seeing Nono-chan nod, I draw my hips back……</t>
+          <t>After seeing Nono-chan nod, he draws his hips back……</t>
         </is>
       </c>
       <c r="C781" t="n">
@@ -12677,7 +12679,7 @@
       </c>
       <c r="B796" s="1" t="inlineStr">
         <is>
-          <t>「Um, e-excuse me… Kikuchiyo…？」</t>
+          <t>Um, e-excuse me… Kikuchiyo…？</t>
         </is>
       </c>
       <c r="C796" t="n">
@@ -13499,7 +13501,7 @@
       </c>
       <c r="B849" s="1" t="inlineStr">
         <is>
-          <t>N-no！ W-what, what should I do...？</t>
+          <t>N-no！ W-what, what should I do...？"</t>
         </is>
       </c>
       <c r="C849" t="n">
